--- a/blog-personal-project/blog-server/src/main/resources/template/数据趋势报表模板.xlsx
+++ b/blog-personal-project/blog-server/src/main/resources/template/数据趋势报表模板.xlsx
@@ -1,35 +1,48 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
-  <bookViews>
-    <workbookView windowHeight="17655"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
-  </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
-</workbook>
+<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <Application>Microsoft Excel Compatible / Openpyxl 3.1.5</Application>
+  <HeadingPairs>
+    <vt:vector size="2" baseType="variant">
+      <vt:variant>
+        <vt:lpstr>工作表</vt:lpstr>
+      </vt:variant>
+      <vt:variant>
+        <vt:i4>3</vt:i4>
+      </vt:variant>
+    </vt:vector>
+  </HeadingPairs>
+  <TitlesOfParts>
+    <vt:vector size="3" baseType="lpstr">
+      <vt:lpstr>Sheet1</vt:lpstr>
+      <vt:lpstr>Sheet2</vt:lpstr>
+      <vt:lpstr>Sheet3</vt:lpstr>
+    </vt:vector>
+  </TitlesOfParts>
+</Properties>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
+<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <cp:lastModifiedBy>小叶同学</cp:lastModifiedBy>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2023-05-12T11:15:00Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-08-23T13:09:42Z</dcterms:modified>
+</cp:coreProperties>
+</file>
+
+<file path=docProps\custom.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="2" name="KSOProductBuildVer">
+    <vt:lpwstr>2052-12.1.0.23125</vt:lpwstr>
+  </property>
+  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="3" name="ICV">
+    <vt:lpwstr>8A8872FEDCFB4BFC92D5EC83903AA71F_12</vt:lpwstr>
+  </property>
+</Properties>
+</file>
+
+<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>数据趋势报表</t>
   </si>
@@ -89,14 +102,11 @@
   </si>
   <si>
     <t>已拒绝友链</t>
-  </si>
-  <si>
-    <t>合计</t>
   </si>
 </sst>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
@@ -887,7 +897,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
   <a:themeElements>
     <a:clrScheme name="WPS">
@@ -1134,10 +1144,39 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
+  <bookViews>
+    <workbookView windowHeight="17655"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+  </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
+</workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B1:I41"/>
+  <dimension ref="B1:I40"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -1499,16 +1538,6 @@
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
       <c r="G40" s="4"/>
-    </row>
-    <row r="41" ht="19" customHeight="1" spans="2:7">
-      <c r="B41" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1522,7 +1551,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
@@ -1534,7 +1563,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
